--- a/data/trans_orig/IP16A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51446</t>
+          <t>51322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59225</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32669</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>39678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34568</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>40059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69418</t>
+          <t>69550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78327</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50316</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57491</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>37391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61634</t>
+          <t>61625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>118705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134127</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234741</t>
+          <t>234869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250734</t>
+          <t>251633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31923</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47672</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58949</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>62468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73574</t>
+          <t>73662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23714</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56369</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64806</t>
+          <t>64765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>37205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>44384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68532</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>79848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58313</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>128442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143967</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247354</t>
+          <t>246860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268237</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22726</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47026</t>
+          <t>46932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31104</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>67821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77187</t>
+          <t>77214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26553</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50305</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>50915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>227854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46622</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>42890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>52594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62029</t>
+          <t>61862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93194</t>
+          <t>93833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103728</t>
+          <t>103578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59636</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75431</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>55801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>112389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129222</t>
+          <t>128993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58782</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>63806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169671</t>
+          <t>169731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165125</t>
+          <t>165638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>176747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>323841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342924</t>
+          <t>343685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6960</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5209</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25283</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21714</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27400</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30758</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27609</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32257</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27218</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32240</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25283</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21309</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27367</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51322</t>
+          <t>51005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58881</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7019</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5119</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8886</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3243</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6951</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38063</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34287</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40066</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36528</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32761</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39678</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32316</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39112</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38063</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>34355</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40059</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1804</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4733</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7851</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27424</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>23360</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20163</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24645</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20431</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24651</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31253</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33703</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>50123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57501</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8273</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2173</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5675</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4178</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8459</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34639</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30544</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37399</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23504</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19825</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24965</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>34639</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37391</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53172</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17356</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9481</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20949</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>129237</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122195</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>134575</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114150</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107949</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>118705</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>108102</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>118405</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>129237</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122970</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>134438</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234869</t>
+          <t>235521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251633</t>
+          <t>250844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9449</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6814</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11748</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29408</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24975</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24632</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19698</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28356</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19266</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28226</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29408</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24711</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32271</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59090</t>
+          <t>58694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11724</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>5992</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10477</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10168</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7076</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12486</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33244</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36690</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31027</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38657</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31336</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38756</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>33244</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27834</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36706</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>73361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41504</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5507</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5487</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9042</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9474</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5884</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33710</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30487</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35393</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27477</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23922</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23490</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30165</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33710</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30110</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35386</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>56748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2761</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10732</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8082</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13227</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13190</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11109</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41140</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36497</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>44468</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>33704</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28559</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37205</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37405</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41140</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36120</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>44384</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>67755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79848</t>
+          <t>79826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13930</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28618</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19150</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34373</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19018</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35328</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14362</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29524</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>129348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144036</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>121326</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113328</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128551</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112373</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128683</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137501</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>128442</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143604</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246860</t>
+          <t>247070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>268221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7928</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2898</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20282</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16248</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22664</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23754</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21461</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21267</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20282</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15905</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22671</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>65,79%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46932</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7562</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7079</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11626</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11072</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3593</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7555</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37554</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33585</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39820</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35620</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31073</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38785</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31627</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38788</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37554</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33592</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39822</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67821</t>
+          <t>67453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77214</t>
+          <t>77384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3151</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3003</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6387</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9953</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21979</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24655</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24612</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21228</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26498</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21419</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26489</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21979</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17853</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>24790</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>50466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4209</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8036</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8625</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -5764,67 +5764,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>27402</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24137</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>28579</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24752</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31326</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24163</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30888</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27402</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24056</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29389</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9561</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20678</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21149</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10447</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>107218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100135</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112512</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>112566</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106783</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117900</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106312</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>107218</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99360</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112829</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210488</t>
+          <t>210470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>227071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5172</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24014</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21363</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23871</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20669</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>24369</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>21273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>48382</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52856</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7187</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>51824</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46719</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54528</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40759</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37055</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42890</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58850</t>
+          <t>33030</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52594</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61862</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>99609</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93833</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103578</t>
+          <t>88539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18198</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45164</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51362</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>69197</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58873</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75201</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53428</t>
+          <t>45640</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>122624</t>
+          <t>94882</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>89226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128993</t>
+          <t>98743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30938</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28511</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28875</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26167</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30031</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61961</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59031</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63806</t>
+          <t>60664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15696</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7984</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>149256</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>160294</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>162702</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>152429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169731</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>172403</t>
+          <t>131080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165638</t>
+          <t>124753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176747</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>335104</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323841</t>
+          <t>279191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343685</t>
+          <t>293780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
